--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487165_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487165_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.657</v>
+        <v>5.4835</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0243</v>
+        <v>6.824</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3673</v>
+        <v>-1.3405</v>
       </c>
       <c r="G2" t="n">
         <v>2.8556</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7933</v>
+        <v>-1.9668</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5671</v>
+        <v>-0.7674</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2262</v>
+        <v>-1.1994</v>
       </c>
       <c r="V2" t="n">
         <v>2.0856</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2145</v>
+        <v>5.4673</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4902</v>
+        <v>6.6091</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2756</v>
+        <v>-1.1418</v>
       </c>
       <c r="G3" t="n">
         <v>6.0992</v>
@@ -688,13 +688,13 @@
         <v>3.0881</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.1079</v>
+        <v>-1.8551</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8196</v>
+        <v>-0.7006</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2883</v>
+        <v>-1.1545</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4416</v>
+        <v>3.513</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7802</v>
+        <v>2.1996</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6614</v>
+        <v>1.3134</v>
       </c>
       <c r="G4" t="n">
         <v>1.5548</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6994</v>
+        <v>-1.628</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1157</v>
+        <v>-0.6963</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5837</v>
+        <v>-0.9317</v>
       </c>
       <c r="V4" t="n">
         <v>1.2702</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0498</v>
+        <v>0.5911</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0388</v>
+        <v>1.0983</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.989</v>
+        <v>-0.5072</v>
       </c>
       <c r="G5" t="n">
         <v>0.1956</v>
@@ -844,13 +844,13 @@
         <v>3.0881</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.1688</v>
+        <v>-2.6274</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6861</v>
+        <v>-0.6266</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.4827</v>
+        <v>-2.0008</v>
       </c>
       <c r="V5" t="n">
         <v>0.8999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1981</v>
+        <v>-0.9115</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5075</v>
+        <v>-1.2477</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3094</v>
+        <v>0.3362</v>
       </c>
       <c r="G6" t="n">
         <v>-1.75</v>
@@ -922,13 +922,13 @@
         <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2201</v>
+        <v>0.0664</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.238</v>
+        <v>0.0218</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5668</v>
+        <v>-1.9019</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.752</v>
+        <v>-0.7926</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8148</v>
+        <v>-1.1092</v>
       </c>
       <c r="G7" t="n">
         <v>0.8858</v>
@@ -1000,13 +1000,13 @@
         <v>2.8951</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.4067</v>
+        <v>-2.7418</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.924</v>
+        <v>-0.9647</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.4827</v>
+        <v>-1.7771</v>
       </c>
       <c r="V7" t="n">
         <v>1.8842</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5859</v>
+        <v>-2.0594</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2761</v>
+        <v>-1.8567</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3098</v>
+        <v>-0.2028</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5138</v>
@@ -1078,13 +1078,13 @@
         <v>1.5441</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6511</v>
+        <v>-1.1247</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9518</v>
+        <v>-0.5324</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6993</v>
+        <v>-0.5923</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.3239</v>
+        <v>-5.899</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7975</v>
+        <v>-3.2387</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5264</v>
+        <v>-2.6602</v>
       </c>
       <c r="G9" t="n">
         <v>-4.0619</v>
@@ -1156,13 +1156,13 @@
         <v>2.1231</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9062</v>
+        <v>-1.4813</v>
       </c>
       <c r="T9" t="n">
-        <v>0.16</v>
+        <v>-0.2812</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0662</v>
+        <v>-1.2001</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5138</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.6882</v>
+        <v>4.283100000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>9.000400000000001</v>
+        <v>9.595300000000002</v>
       </c>
       <c r="F10" t="n">
         <v>-5.3121</v>
@@ -1234,10 +1234,10 @@
         <v>18.3357</v>
       </c>
       <c r="S10" t="n">
-        <v>-13.9535</v>
+        <v>-13.3587</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.142300000000001</v>
+        <v>-4.5474</v>
       </c>
       <c r="U10" t="n">
         <v>-8.811299999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.7997</v>
+        <v>3.01</v>
       </c>
       <c r="E11" t="n">
-        <v>5.7397</v>
+        <v>4.1375</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9401</v>
+        <v>-1.1275</v>
       </c>
       <c r="G11" t="n">
         <v>0.6973</v>
@@ -1312,13 +1312,13 @@
         <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4174</v>
+        <v>2.6278</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3063</v>
+        <v>1.7041</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1111</v>
+        <v>0.9237</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5081</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2395</v>
+        <v>2.0212</v>
       </c>
       <c r="E12" t="n">
-        <v>3.768</v>
+        <v>2.1658</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4715</v>
+        <v>-0.1446</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5447</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>5.7665</v>
+        <v>3.5482</v>
       </c>
       <c r="T12" t="n">
-        <v>3.81</v>
+        <v>2.2078</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9565</v>
+        <v>1.3404</v>
       </c>
       <c r="V12" t="n">
         <v>1.3339</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>P. SOUZA FIGUEIREDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9127999999999999</v>
+        <v>1.2308</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4692</v>
+        <v>1.7807</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5564</v>
+        <v>-0.5498</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1242</v>
+        <v>2.6316</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.1681</v>
+        <v>1.8484</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0439</v>
+        <v>0.7833</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3959</v>
+        <v>3.9454</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0713</v>
+        <v>2.7166</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6755</v>
+        <v>1.2288</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7283</v>
+        <v>-1.3138</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0968</v>
+        <v>-0.8682</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3684</v>
+        <v>-0.4456</v>
       </c>
       <c r="P13" t="n">
-        <v>0.579</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R13" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5957</v>
+        <v>1.9602</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5792</v>
+        <v>1.0814</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0165</v>
+        <v>0.8787</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1377</v>
+        <v>-0.4658</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2859</v>
+        <v>0.614</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4236</v>
+        <v>-1.0798</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. MIGUEL PEREZ DEL NOTARIO</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8552</v>
+        <v>0.5466</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7944</v>
+        <v>1.568</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0608</v>
+        <v>-1.0214</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1152</v>
+        <v>-2.1242</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1087</v>
+        <v>-3.1681</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0064</v>
+        <v>1.0439</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3053</v>
+        <v>-0.3959</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3053</v>
+        <v>-1.0713</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.6755</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4204</v>
+        <v>-1.7283</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.414</v>
+        <v>-2.0968</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0064</v>
+        <v>0.3684</v>
       </c>
       <c r="P14" t="n">
         <v>0.579</v>
@@ -1546,28 +1546,28 @@
         <v>0.579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3913</v>
+        <v>2.2295</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4891</v>
+        <v>1.678</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0978</v>
+        <v>0.5516</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.1377</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.4236</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. SOUZA FIGUEIREDO</t>
+          <t>E. MIGUEL PEREZ DEL NOTARIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3765</v>
+        <v>0.5082</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9795</v>
+        <v>0.3938</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.603</v>
+        <v>0.1143</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6316</v>
+        <v>-0.1152</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8484</v>
+        <v>-0.1087</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7833</v>
+        <v>-0.0064</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9454</v>
+        <v>0.3053</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7166</v>
+        <v>0.3053</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2288</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3138</v>
+        <v>-0.4204</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8682</v>
+        <v>-0.414</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4456</v>
+        <v>-0.0064</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.8951</v>
+        <v>0.579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1058</v>
+        <v>0.0443</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2803</v>
+        <v>0.0886</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8255</v>
+        <v>-0.0443</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4658</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3033</v>
+        <v>-0.2348</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6887</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3855</v>
+        <v>0.6528</v>
       </c>
       <c r="G16" t="n">
         <v>-1.912</v>
@@ -1702,13 +1702,13 @@
         <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0297</v>
+        <v>1.0982</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2234</v>
+        <v>0.5777</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2531</v>
+        <v>0.5205</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.1463</v>
+        <v>-1.2159</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.866</v>
+        <v>-0.3639</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2803</v>
+        <v>-0.852</v>
       </c>
       <c r="G17" t="n">
         <v>1.5994</v>
@@ -1780,13 +1780,13 @@
         <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6055</v>
+        <v>1.325</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8037</v>
+        <v>0.6984</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1983</v>
+        <v>0.6266</v>
       </c>
       <c r="V17" t="n">
         <v>0.1059</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.2034</v>
+        <v>-2.9343</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7703</v>
+        <v>-1.7689</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4332</v>
+        <v>-1.1655</v>
       </c>
       <c r="G18" t="n">
         <v>-0.243</v>
@@ -1858,13 +1858,13 @@
         <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8024</v>
+        <v>0.4667</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7733</v>
+        <v>0.2281</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0291</v>
+        <v>0.2386</v>
       </c>
       <c r="V18" t="n">
         <v>-1.228</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.219</v>
+        <v>-5.9526</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3417</v>
+        <v>-2.9412</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8772</v>
+        <v>-3.0114</v>
       </c>
       <c r="G19" t="n">
         <v>-4.2546</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0549</v>
+        <v>1.3213</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1468</v>
+        <v>0.5473</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9082</v>
+        <v>0.774</v>
       </c>
       <c r="V19" t="n">
         <v>-2.8263</v>
@@ -1969,19 +1969,19 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.688300000000003</v>
+        <v>-3.0208</v>
       </c>
       <c r="E20" t="n">
-        <v>4.084099999999999</v>
+        <v>4.084200000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.7724</v>
+        <v>-7.1051</v>
       </c>
       <c r="G20" t="n">
         <v>-4.2654</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7663999999999997</v>
+        <v>-0.7664</v>
       </c>
       <c r="I20" t="n">
         <v>-3.4987</v>
@@ -2014,13 +2014,13 @@
         <v>8.6852</v>
       </c>
       <c r="S20" t="n">
-        <v>13.9534</v>
+        <v>14.6212</v>
       </c>
       <c r="T20" t="n">
-        <v>8.811300000000001</v>
+        <v>8.811400000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>5.1423</v>
+        <v>5.8098</v>
       </c>
       <c r="V20" t="n">
         <v>-3.7261</v>
